--- a/output/pdf_financials_xlsx/HRK.xlsx
+++ b/output/pdf_financials_xlsx/HRK.xlsx
@@ -1917,10 +1917,10 @@
         <v>0</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>-0.053967</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.053967</v>
       </c>
     </row>
     <row r="92">
@@ -1930,13 +1930,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.039264</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.208564</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.208564</v>
       </c>
     </row>
     <row r="93">
@@ -3083,7 +3083,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
         <v>0.039264</v>
       </c>
@@ -3141,7 +3145,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HRK.xlsx
+++ b/output/pdf_financials_xlsx/HRK.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.130211</v>
+        <v>0.216943</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.411496</v>
+        <v>0.522297</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.07808</v>
+        <v>0.146749</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.130211</v>
+        <v>-0.216943</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.411496</v>
+        <v>-0.522297</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.07808</v>
+        <v>-0.146749</v>
       </c>
     </row>
     <row r="12">
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003099</v>
       </c>
     </row>
     <row r="13">
@@ -869,7 +869,7 @@
         <v>-0.429158</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.128336</v>
+        <v>-0.131435</v>
       </c>
     </row>
     <row r="28">
@@ -901,7 +901,7 @@
         <v>-0.429158</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.128336</v>
+        <v>-0.131435</v>
       </c>
     </row>
     <row r="30">
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.089945</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.022401</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.013036</v>
       </c>
     </row>
     <row r="35">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.089945</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.022401</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.013036</v>
       </c>
     </row>
     <row r="37">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.096277</v>
+        <v>0.006332</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.031834</v>
+        <v>0.009433</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.423728</v>
+        <v>0.410692</v>
       </c>
     </row>
     <row r="49">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
@@ -4797,17 +4797,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>-0.216943</v>
+        <v>0.216943</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>-0.522297</v>
+        <v>0.522297</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>-0.146749</v>
+        <v>0.146749</v>
       </c>
     </row>
     <row r="69">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">

--- a/output/pdf_financials_xlsx/HRK.xlsx
+++ b/output/pdf_financials_xlsx/HRK.xlsx
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="C67" s="3" t="n">
         <v>0.096529</v>
